--- a/artfynd/A 31207-2022 artfynd.xlsx
+++ b/artfynd/A 31207-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31207-2022 artfynd.xlsx
+++ b/artfynd/A 31207-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56442829</v>
+        <v>69506593</v>
       </c>
       <c r="B2" t="n">
-        <v>88896</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>720</v>
+        <v>473</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Bon</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lugnet 2,5 km NV om Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680349.6406553154</v>
+        <v>680373</v>
       </c>
       <c r="R2" t="n">
-        <v>6689470.460554018</v>
+        <v>6689436</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +752,14 @@
           <t>2004-07-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2004-07-28</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>En halv häxring, 2 m i diameter, under äldre gran.</t>
+          <t>2 ex. i äldre, fuktigt granskogsparti.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre, örtrik granskog.</t>
+          <t>Äldre, örtrik barrskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,42 +791,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69506946</v>
+        <v>69506594</v>
       </c>
       <c r="B3" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3674</v>
+        <v>473</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -846,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680418.8612136451</v>
+        <v>680224</v>
       </c>
       <c r="R3" t="n">
-        <v>6689317.993105282</v>
+        <v>6689526</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,27 +865,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2004-07-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-09-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2004-07-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-09-08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Ca. 15 ex.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,59 +907,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69506593</v>
+        <v>56442829</v>
       </c>
       <c r="B4" t="n">
-        <v>85222</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>473</v>
+        <v>720</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bon</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lugnet 2,5 km NV om Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680373.2103674763</v>
+        <v>680350</v>
       </c>
       <c r="R4" t="n">
-        <v>6689436.37820774</v>
+        <v>6689470</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,24 +975,14 @@
           <t>2004-07-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2004-07-28</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2 ex. i äldre, fuktigt granskogsparti.</t>
+          <t>En halv häxring, 2 m i diameter, under äldre gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,7 +996,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Äldre, örtrik barrskog.</t>
+          <t>Äldre, örtrik granskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1059,59 +1014,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69506949</v>
+        <v>56442982</v>
       </c>
       <c r="B5" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>720</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lugnet 2,5 km NV om Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680310.4367417367</v>
+        <v>680531</v>
       </c>
       <c r="R5" t="n">
-        <v>6689488.874136376</v>
+        <v>6689209</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1141,24 +1082,14 @@
           <t>2004-07-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2004-07-28</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1 ex.</t>
+          <t>Två halva häxringar, båda 4 m i diameter, under äldre gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,7 +1103,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre, örtrik barrskog.</t>
+          <t>Äldre, örtrik granskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1190,42 +1121,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69506594</v>
+        <v>69506945</v>
       </c>
       <c r="B6" t="n">
-        <v>85222</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>473</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1239,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680224.0684823942</v>
+        <v>680508</v>
       </c>
       <c r="R6" t="n">
-        <v>6689525.804523568</v>
+        <v>6689179</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1269,27 +1195,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2004-09-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-07-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2004-09-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-07-28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ca. 15 ex.</t>
+          <t>1 ex.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1321,15 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69506947</v>
+        <v>69506946</v>
       </c>
       <c r="B7" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1267,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1370,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680418.3267551056</v>
+        <v>680419</v>
       </c>
       <c r="R7" t="n">
-        <v>6689198.308557922</v>
+        <v>6689318</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1403,24 +1314,14 @@
           <t>2004-07-28</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2004-07-28</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 ex.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1452,15 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>69506948</v>
+        <v>69506947</v>
       </c>
       <c r="B8" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680375.5766576977</v>
+        <v>680418</v>
       </c>
       <c r="R8" t="n">
-        <v>6689408.69236328</v>
+        <v>6689198</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1534,19 +1430,9 @@
           <t>2004-07-28</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2004-07-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1583,15 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>69524755</v>
+        <v>69506948</v>
       </c>
       <c r="B9" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,26 +1480,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>3674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1632,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680262.2793645296</v>
+        <v>680376</v>
       </c>
       <c r="R9" t="n">
-        <v>6689507.341127324</v>
+        <v>6689409</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1665,24 +1546,14 @@
           <t>2004-07-28</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2004-07-28</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ca. 10 ex.</t>
+          <t>1 ex.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1714,15 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>69547503</v>
+        <v>69506949</v>
       </c>
       <c r="B10" t="n">
-        <v>84795</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,21 +1596,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>236437</v>
+        <v>3674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1763,10 +1629,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680415.8566808513</v>
+        <v>680310</v>
       </c>
       <c r="R10" t="n">
-        <v>6689218.046688485</v>
+        <v>6689489</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1796,19 +1662,9 @@
           <t>2004-07-28</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2004-07-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1845,42 +1701,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>75905838</v>
+        <v>69524755</v>
       </c>
       <c r="B11" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1894,10 +1745,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680314.5034848364</v>
+        <v>680262</v>
       </c>
       <c r="R11" t="n">
-        <v>6689487.089661532</v>
+        <v>6689507</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1927,24 +1778,14 @@
           <t>2004-07-28</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2004-07-28</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Ca. 10 ex.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1976,15 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>75972671</v>
+        <v>75905838</v>
       </c>
       <c r="B12" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1992,31 +1828,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219795</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2025,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680248.8287301473</v>
+        <v>680315</v>
       </c>
       <c r="R12" t="n">
-        <v>6689537.952634537</v>
+        <v>6689487</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2058,24 +1894,14 @@
           <t>2004-07-28</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2004-07-28</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1 planta.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2086,6 +1912,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik barrskog.</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2102,59 +1933,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>76100783</v>
+        <v>76127169</v>
       </c>
       <c r="B13" t="n">
-        <v>103252</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224098</v>
+        <v>219711</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Wallr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lugnet 2,5 km NV om Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680429.6423187311</v>
+        <v>680375</v>
       </c>
       <c r="R13" t="n">
-        <v>6689301.149887978</v>
+        <v>6689261</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2181,27 +1998,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2004-07-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-11-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2004-07-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-11-28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2 stjälkar.</t>
+          <t>Litet bestånd.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2228,15 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>76127169</v>
+        <v>75972671</v>
       </c>
       <c r="B14" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99017</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2244,34 +2046,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219711</v>
+        <v>219795</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lugnet 2,5 km NV om Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680375.4474169519</v>
+        <v>680249</v>
       </c>
       <c r="R14" t="n">
-        <v>6689260.730310176</v>
+        <v>6689538</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2298,27 +2109,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2006-11-28</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-07-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2006-11-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-07-28</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Litet bestånd.</t>
+          <t>1 planta.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2342,6 +2143,344 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>76097880</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lugnet 2,5 km NV om Norrskedika, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>680507</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6689184</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2004-07-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2004-07-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 planta.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>76100783</v>
+      </c>
+      <c r="B16" t="n">
+        <v>106231</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lugnet 2,5 km NV om Norrskedika, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>680430</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6689301</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2004-07-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2004-07-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2 stjälkar.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>69547503</v>
+      </c>
+      <c r="B17" t="n">
+        <v>89870</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>236437</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brun klibbskivling</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Limacella glioderma</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Maire</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lugnet 2,5 km NV om Norrskedika, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>680416</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6689218</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2004-07-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2004-07-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1 ex.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31207-2022 artfynd.xlsx
+++ b/artfynd/A 31207-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506593</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506594</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56442829</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56442982</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506945</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506946</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1466,6 +1501,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506947</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1582,6 +1622,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506948</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1698,6 +1743,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506949</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1814,6 +1864,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69524755</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1930,6 +1985,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75905838</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2032,6 +2092,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76127169</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2143,6 +2208,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75972671</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2254,6 +2324,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76097880</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2365,6 +2440,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76100783</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2481,8 +2561,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69547503</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>